--- a/Data/EXCEL/Transfer/salemon/202208/4749-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/4749-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9463329-A9FE-4102-89B1-A13C7D8149D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5352D93-AE92-417A-A43B-FEC6197C8283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="4749-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,18 +1226,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="10" max="13" width="9.875" customWidth="1"/>
-    <col min="14" max="15" width="9.375" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
+    <col min="10" max="13" width="14" customWidth="1"/>
+    <col min="14" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1382,378 +1390,378 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>161.5</v>
+        <v>181.5</v>
       </c>
       <c r="C5" s="7">
-        <v>181.5</v>
+        <v>289</v>
       </c>
       <c r="D5" s="7">
-        <v>182.5</v>
+        <v>293.5</v>
       </c>
       <c r="E5" s="7">
-        <v>144.5</v>
+        <v>174</v>
       </c>
       <c r="F5" s="8">
-        <v>20</v>
+        <v>107.5</v>
       </c>
       <c r="G5" s="8">
-        <v>12.38</v>
+        <v>59.23</v>
       </c>
       <c r="H5" s="9">
-        <v>2.14</v>
-      </c>
-      <c r="I5" s="8">
-        <v>10.199999999999999</v>
+        <v>2.04</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-4.3099999999999996</v>
       </c>
       <c r="J5" s="8">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="K5" s="9">
-        <v>11.8</v>
+        <v>13.85</v>
       </c>
       <c r="L5" s="8">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="M5" s="9">
-        <v>2.14</v>
-      </c>
-      <c r="N5" s="8">
-        <v>10.199999999999999</v>
+        <v>2.04</v>
+      </c>
+      <c r="N5" s="10">
+        <v>-4.3099999999999996</v>
       </c>
       <c r="O5" s="8">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="P5" s="9">
-        <v>11.8</v>
+        <v>13.85</v>
       </c>
       <c r="Q5" s="8">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>148.5</v>
+        <v>161.5</v>
       </c>
       <c r="C6" s="7">
-        <v>161.5</v>
+        <v>181.5</v>
       </c>
       <c r="D6" s="7">
-        <v>180</v>
+        <v>182.5</v>
       </c>
       <c r="E6" s="7">
-        <v>148</v>
+        <v>144.5</v>
       </c>
       <c r="F6" s="8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8">
-        <v>8.75</v>
+        <v>12.38</v>
       </c>
       <c r="H6" s="9">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="I6" s="8">
-        <v>2.2799999999999998</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J6" s="8">
+        <v>38.5</v>
+      </c>
+      <c r="K6" s="9">
+        <v>11.8</v>
+      </c>
+      <c r="L6" s="8">
         <v>31.4</v>
       </c>
-      <c r="K6" s="9">
-        <v>9.67</v>
-      </c>
-      <c r="L6" s="8">
-        <v>29.9</v>
-      </c>
       <c r="M6" s="9">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="N6" s="8">
-        <v>2.2799999999999998</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="O6" s="8">
+        <v>38.5</v>
+      </c>
+      <c r="P6" s="9">
+        <v>11.8</v>
+      </c>
+      <c r="Q6" s="8">
         <v>31.4</v>
-      </c>
-      <c r="P6" s="9">
-        <v>9.67</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>29.9</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>117</v>
+        <v>148.5</v>
       </c>
       <c r="C7" s="7">
-        <v>148.5</v>
+        <v>161.5</v>
       </c>
       <c r="D7" s="7">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E7" s="7">
-        <v>112.5</v>
+        <v>148</v>
       </c>
       <c r="F7" s="8">
-        <v>31.5</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8">
-        <v>26.92</v>
+        <v>8.75</v>
       </c>
       <c r="H7" s="9">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="I7" s="8">
-        <v>33</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="J7" s="8">
-        <v>40.299999999999997</v>
+        <v>31.4</v>
       </c>
       <c r="K7" s="9">
-        <v>7.73</v>
+        <v>9.67</v>
       </c>
       <c r="L7" s="8">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="M7" s="9">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="N7" s="8">
-        <v>33</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="O7" s="8">
-        <v>40.299999999999997</v>
+        <v>31.4</v>
       </c>
       <c r="P7" s="9">
-        <v>7.73</v>
+        <v>9.67</v>
       </c>
       <c r="Q7" s="8">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C8" s="7">
-        <v>117</v>
+        <v>148.5</v>
       </c>
       <c r="D8" s="7">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E8" s="7">
-        <v>103.5</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-26</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-18.18</v>
+        <v>112.5</v>
+      </c>
+      <c r="F8" s="8">
+        <v>31.5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>26.92</v>
       </c>
       <c r="H8" s="9">
-        <v>1.42</v>
-      </c>
-      <c r="I8" s="10">
-        <v>-7.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="I8" s="8">
+        <v>33</v>
       </c>
       <c r="J8" s="8">
-        <v>16.600000000000001</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="K8" s="9">
-        <v>5.83</v>
+        <v>7.73</v>
       </c>
       <c r="L8" s="8">
-        <v>26.4</v>
+        <v>29.5</v>
       </c>
       <c r="M8" s="9">
-        <v>1.42</v>
-      </c>
-      <c r="N8" s="10">
-        <v>-7.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="N8" s="8">
+        <v>33</v>
       </c>
       <c r="O8" s="8">
-        <v>16.600000000000001</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="P8" s="9">
-        <v>5.83</v>
+        <v>7.73</v>
       </c>
       <c r="Q8" s="8">
-        <v>26.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C9" s="7">
+        <v>117</v>
+      </c>
+      <c r="D9" s="7">
         <v>143</v>
       </c>
-      <c r="D9" s="7">
-        <v>162.5</v>
-      </c>
       <c r="E9" s="7">
-        <v>136</v>
+        <v>103.5</v>
       </c>
       <c r="F9" s="10">
-        <v>-8</v>
+        <v>-26</v>
       </c>
       <c r="G9" s="10">
-        <v>-5.3</v>
+        <v>-18.18</v>
       </c>
       <c r="H9" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="I9" s="8">
-        <v>11.6</v>
+        <v>1.42</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-7.39</v>
       </c>
       <c r="J9" s="8">
-        <v>14</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="K9" s="9">
-        <v>4.41</v>
+        <v>5.83</v>
       </c>
       <c r="L9" s="8">
-        <v>29.9</v>
+        <v>26.4</v>
       </c>
       <c r="M9" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="N9" s="8">
-        <v>11.6</v>
+        <v>1.42</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-7.39</v>
       </c>
       <c r="O9" s="8">
-        <v>14</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="P9" s="9">
-        <v>4.41</v>
+        <v>5.83</v>
       </c>
       <c r="Q9" s="8">
-        <v>29.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>3.2</v>
+        <v>151</v>
       </c>
       <c r="C10" s="7">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D10" s="7">
-        <v>171.5</v>
+        <v>162.5</v>
       </c>
       <c r="E10" s="7">
-        <v>133.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>147.80000000000001</v>
-      </c>
-      <c r="G10" s="8">
-        <v>4618.75</v>
+        <v>136</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-8</v>
+      </c>
+      <c r="G10" s="10">
+        <v>-5.3</v>
       </c>
       <c r="H10" s="9">
-        <v>1.38</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-7.29</v>
+        <v>1.54</v>
+      </c>
+      <c r="I10" s="8">
+        <v>11.6</v>
       </c>
       <c r="J10" s="8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K10" s="9">
-        <v>2.87</v>
+        <v>4.41</v>
       </c>
       <c r="L10" s="8">
-        <v>40.5</v>
+        <v>29.9</v>
       </c>
       <c r="M10" s="9">
-        <v>1.38</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-7.29</v>
+        <v>1.54</v>
+      </c>
+      <c r="N10" s="8">
+        <v>11.6</v>
       </c>
       <c r="O10" s="8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="P10" s="9">
-        <v>2.87</v>
+        <v>4.41</v>
       </c>
       <c r="Q10" s="8">
-        <v>40.5</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
+        <v>44593</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="C11" s="7">
+        <v>151</v>
+      </c>
+      <c r="D11" s="7">
+        <v>171.5</v>
+      </c>
+      <c r="E11" s="7">
+        <v>133.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4618.75</v>
       </c>
       <c r="H11" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1.67</v>
+        <v>1.38</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-7.29</v>
       </c>
       <c r="J11" s="8">
-        <v>55.7</v>
+        <v>27</v>
       </c>
       <c r="K11" s="9">
-        <v>1.49</v>
+        <v>2.87</v>
       </c>
       <c r="L11" s="8">
-        <v>55.7</v>
+        <v>40.5</v>
       </c>
       <c r="M11" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="N11" s="8">
-        <v>1.67</v>
+        <v>1.38</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-7.29</v>
       </c>
       <c r="O11" s="8">
-        <v>55.7</v>
+        <v>27</v>
       </c>
       <c r="P11" s="9">
-        <v>1.49</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" s="8">
-        <v>55.7</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1774,39 +1782,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="9">
-        <v>1.46</v>
-      </c>
-      <c r="I12" s="10">
-        <v>-0.82</v>
+        <v>1.49</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1.67</v>
       </c>
       <c r="J12" s="8">
-        <v>7.87</v>
+        <v>55.7</v>
       </c>
       <c r="K12" s="9">
-        <v>16.04</v>
+        <v>1.49</v>
       </c>
       <c r="L12" s="8">
-        <v>38.9</v>
+        <v>55.7</v>
       </c>
       <c r="M12" s="9">
-        <v>1.46</v>
-      </c>
-      <c r="N12" s="10">
-        <v>-0.82</v>
+        <v>1.49</v>
+      </c>
+      <c r="N12" s="8">
+        <v>1.67</v>
       </c>
       <c r="O12" s="8">
-        <v>7.87</v>
+        <v>55.7</v>
       </c>
       <c r="P12" s="9">
-        <v>16.04</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" s="8">
-        <v>38.9</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1827,39 +1835,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="I13" s="8">
-        <v>8.94</v>
+        <v>1.46</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-0.82</v>
       </c>
       <c r="J13" s="8">
-        <v>22.1</v>
+        <v>7.87</v>
       </c>
       <c r="K13" s="9">
-        <v>14.57</v>
+        <v>16.04</v>
       </c>
       <c r="L13" s="8">
-        <v>43</v>
+        <v>38.9</v>
       </c>
       <c r="M13" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="N13" s="8">
-        <v>8.94</v>
+        <v>1.46</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-0.82</v>
       </c>
       <c r="O13" s="8">
-        <v>22.1</v>
+        <v>7.87</v>
       </c>
       <c r="P13" s="9">
-        <v>14.57</v>
+        <v>16.04</v>
       </c>
       <c r="Q13" s="8">
-        <v>43</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1880,39 +1888,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>1.35</v>
-      </c>
-      <c r="I14" s="10">
-        <v>-0.65</v>
+        <v>1.48</v>
+      </c>
+      <c r="I14" s="8">
+        <v>8.94</v>
       </c>
       <c r="J14" s="8">
-        <v>70.5</v>
+        <v>22.1</v>
       </c>
       <c r="K14" s="9">
-        <v>13.1</v>
+        <v>14.57</v>
       </c>
       <c r="L14" s="8">
-        <v>45.9</v>
+        <v>43</v>
       </c>
       <c r="M14" s="9">
-        <v>1.35</v>
-      </c>
-      <c r="N14" s="10">
-        <v>-0.65</v>
+        <v>1.48</v>
+      </c>
+      <c r="N14" s="8">
+        <v>8.94</v>
       </c>
       <c r="O14" s="8">
-        <v>70.5</v>
+        <v>22.1</v>
       </c>
       <c r="P14" s="9">
-        <v>13.1</v>
+        <v>14.57</v>
       </c>
       <c r="Q14" s="8">
-        <v>45.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1933,39 +1941,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="I15" s="10">
-        <v>-6.5</v>
+        <v>-0.65</v>
       </c>
       <c r="J15" s="8">
-        <v>45.2</v>
+        <v>70.5</v>
       </c>
       <c r="K15" s="9">
-        <v>11.74</v>
+        <v>13.1</v>
       </c>
       <c r="L15" s="8">
-        <v>43.5</v>
+        <v>45.9</v>
       </c>
       <c r="M15" s="9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N15" s="10">
-        <v>-6.5</v>
+        <v>-0.65</v>
       </c>
       <c r="O15" s="8">
-        <v>45.2</v>
+        <v>70.5</v>
       </c>
       <c r="P15" s="9">
-        <v>11.74</v>
+        <v>13.1</v>
       </c>
       <c r="Q15" s="8">
-        <v>43.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1986,39 +1994,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>1.46</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>17</v>
+        <v>1.36</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-6.5</v>
       </c>
       <c r="J16" s="8">
-        <v>51.8</v>
+        <v>45.2</v>
       </c>
       <c r="K16" s="9">
-        <v>10.38</v>
+        <v>11.74</v>
       </c>
       <c r="L16" s="8">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="M16" s="9">
-        <v>1.46</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>17</v>
+        <v>1.36</v>
+      </c>
+      <c r="N16" s="10">
+        <v>-6.5</v>
       </c>
       <c r="O16" s="8">
-        <v>51.8</v>
+        <v>45.2</v>
       </c>
       <c r="P16" s="9">
-        <v>10.38</v>
+        <v>11.74</v>
       </c>
       <c r="Q16" s="8">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>42552</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2039,39 +2047,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="9">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="I17" s="10">
-        <v>-9.1999999999999993</v>
-      </c>
-      <c r="J17" s="10">
-        <v>-14.2</v>
+        <v>1.46</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="8">
+        <v>52.5</v>
       </c>
       <c r="K17" s="9">
-        <v>5.8</v>
-      </c>
-      <c r="L17" s="10">
-        <v>-4.18</v>
+        <v>10.45</v>
+      </c>
+      <c r="L17" s="8">
+        <v>44.2</v>
       </c>
       <c r="M17" s="9">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="N17" s="10">
-        <v>-9.1999999999999993</v>
-      </c>
-      <c r="O17" s="10">
-        <v>-14.2</v>
+        <v>1.46</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O17" s="8">
+        <v>52.5</v>
       </c>
       <c r="P17" s="9">
-        <v>5.8</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>-4.18</v>
+        <v>10.45</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>44.2</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2092,39 +2100,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="I18" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="J18" s="8">
-        <v>6.33</v>
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="I18" s="10">
+        <v>-9.1999999999999993</v>
+      </c>
+      <c r="J18" s="10">
+        <v>-14.2</v>
       </c>
       <c r="K18" s="9">
-        <v>4.93</v>
+        <v>5.8</v>
       </c>
       <c r="L18" s="10">
-        <v>-2.1800000000000002</v>
+        <v>-4.18</v>
       </c>
       <c r="M18" s="9">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="N18" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="O18" s="8">
-        <v>6.33</v>
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="N18" s="10">
+        <v>-9.1999999999999993</v>
+      </c>
+      <c r="O18" s="10">
+        <v>-14.2</v>
       </c>
       <c r="P18" s="9">
-        <v>4.93</v>
+        <v>5.8</v>
       </c>
       <c r="Q18" s="10">
-        <v>-2.1800000000000002</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2145,39 +2153,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
-        <v>0.86699999999999999</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="I19" s="8">
-        <v>0.86</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J19" s="8">
-        <v>8.25</v>
+        <v>6.33</v>
       </c>
       <c r="K19" s="9">
-        <v>3.98</v>
+        <v>4.93</v>
       </c>
       <c r="L19" s="10">
-        <v>-4.0199999999999996</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="M19" s="9">
-        <v>0.86699999999999999</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="N19" s="8">
-        <v>0.86</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="O19" s="8">
-        <v>8.25</v>
+        <v>6.33</v>
       </c>
       <c r="P19" s="9">
-        <v>3.98</v>
+        <v>4.93</v>
       </c>
       <c r="Q19" s="10">
-        <v>-4.0199999999999996</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2198,39 +2206,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="I20" s="8">
         <v>0.86</v>
       </c>
-      <c r="I20" s="8">
-        <v>5.49</v>
-      </c>
       <c r="J20" s="8">
-        <v>8.6199999999999992</v>
+        <v>8.25</v>
       </c>
       <c r="K20" s="9">
-        <v>3.11</v>
+        <v>3.98</v>
       </c>
       <c r="L20" s="10">
-        <v>-6.97</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="M20" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="N20" s="8">
         <v>0.86</v>
       </c>
-      <c r="N20" s="8">
-        <v>5.49</v>
-      </c>
       <c r="O20" s="8">
-        <v>8.6199999999999992</v>
+        <v>8.25</v>
       </c>
       <c r="P20" s="9">
-        <v>3.11</v>
+        <v>3.98</v>
       </c>
       <c r="Q20" s="10">
-        <v>-6.97</v>
+        <v>-4.0199999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2251,39 +2259,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="9">
-        <v>0.81499999999999995</v>
+        <v>0.86</v>
       </c>
       <c r="I21" s="8">
-        <v>45.4</v>
-      </c>
-      <c r="J21" s="10">
-        <v>-5.14</v>
+        <v>5.49</v>
+      </c>
+      <c r="J21" s="8">
+        <v>8.6199999999999992</v>
       </c>
       <c r="K21" s="9">
-        <v>2.25</v>
+        <v>3.11</v>
       </c>
       <c r="L21" s="10">
-        <v>-11.8</v>
+        <v>-6.97</v>
       </c>
       <c r="M21" s="9">
-        <v>0.81499999999999995</v>
+        <v>0.86</v>
       </c>
       <c r="N21" s="8">
-        <v>45.4</v>
-      </c>
-      <c r="O21" s="10">
-        <v>-5.14</v>
+        <v>5.49</v>
+      </c>
+      <c r="O21" s="8">
+        <v>8.6199999999999992</v>
       </c>
       <c r="P21" s="9">
-        <v>2.25</v>
+        <v>3.11</v>
       </c>
       <c r="Q21" s="10">
-        <v>-11.8</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2304,39 +2312,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I22" s="10">
-        <v>-36.1</v>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="I22" s="8">
+        <v>45.4</v>
       </c>
       <c r="J22" s="10">
-        <v>-26.8</v>
+        <v>-5.14</v>
       </c>
       <c r="K22" s="9">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="L22" s="10">
-        <v>-15.2</v>
+        <v>-11.8</v>
       </c>
       <c r="M22" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="N22" s="10">
-        <v>-36.1</v>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="N22" s="8">
+        <v>45.4</v>
       </c>
       <c r="O22" s="10">
-        <v>-26.8</v>
+        <v>-5.14</v>
       </c>
       <c r="P22" s="9">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" s="10">
-        <v>-15.2</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2357,39 +2365,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="9">
-        <v>0.877</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I23" s="10">
-        <v>-7.58</v>
+        <v>-36.1</v>
       </c>
       <c r="J23" s="10">
-        <v>-5.62</v>
+        <v>-26.8</v>
       </c>
       <c r="K23" s="9">
-        <v>0.877</v>
+        <v>1.44</v>
       </c>
       <c r="L23" s="10">
-        <v>-5.62</v>
+        <v>-15.2</v>
       </c>
       <c r="M23" s="9">
-        <v>0.877</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="N23" s="10">
-        <v>-7.58</v>
+        <v>-36.1</v>
       </c>
       <c r="O23" s="10">
-        <v>-5.62</v>
+        <v>-26.8</v>
       </c>
       <c r="P23" s="9">
-        <v>0.877</v>
+        <v>1.44</v>
       </c>
       <c r="Q23" s="10">
-        <v>-5.62</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2410,39 +2418,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="9">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="I24" s="8">
-        <v>4.22</v>
+        <v>0.877</v>
+      </c>
+      <c r="I24" s="10">
+        <v>-7.58</v>
       </c>
       <c r="J24" s="10">
-        <v>-5.34</v>
+        <v>-5.62</v>
       </c>
       <c r="K24" s="9">
-        <v>10.5</v>
+        <v>0.877</v>
       </c>
       <c r="L24" s="10">
-        <v>-10.9</v>
+        <v>-5.62</v>
       </c>
       <c r="M24" s="9">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="N24" s="8">
-        <v>4.22</v>
+        <v>0.877</v>
+      </c>
+      <c r="N24" s="10">
+        <v>-7.58</v>
       </c>
       <c r="O24" s="10">
-        <v>-5.34</v>
+        <v>-5.62</v>
       </c>
       <c r="P24" s="9">
-        <v>10.5</v>
+        <v>0.877</v>
       </c>
       <c r="Q24" s="10">
-        <v>-10.9</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2463,39 +2471,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="9">
-        <v>0.91</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="I25" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="J25" s="8">
-        <v>13.1</v>
+        <v>4.22</v>
+      </c>
+      <c r="J25" s="10">
+        <v>-5.34</v>
       </c>
       <c r="K25" s="9">
-        <v>9.5500000000000007</v>
+        <v>10.5</v>
       </c>
       <c r="L25" s="10">
-        <v>-11.4</v>
+        <v>-10.9</v>
       </c>
       <c r="M25" s="9">
-        <v>0.91</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="N25" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="O25" s="8">
-        <v>13.1</v>
+        <v>4.22</v>
+      </c>
+      <c r="O25" s="10">
+        <v>-5.34</v>
       </c>
       <c r="P25" s="9">
-        <v>9.5500000000000007</v>
+        <v>10.5</v>
       </c>
       <c r="Q25" s="10">
-        <v>-11.4</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2516,39 +2524,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>0.90600000000000003</v>
+        <v>0.91</v>
       </c>
       <c r="I26" s="8">
-        <v>3.99</v>
-      </c>
-      <c r="J26" s="10">
-        <v>-9.36</v>
+        <v>0.44</v>
+      </c>
+      <c r="J26" s="8">
+        <v>13.1</v>
       </c>
       <c r="K26" s="9">
-        <v>8.64</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="L26" s="10">
-        <v>-13.4</v>
+        <v>-11.4</v>
       </c>
       <c r="M26" s="9">
-        <v>0.90600000000000003</v>
+        <v>0.91</v>
       </c>
       <c r="N26" s="8">
-        <v>3.99</v>
-      </c>
-      <c r="O26" s="10">
-        <v>-9.36</v>
+        <v>0.44</v>
+      </c>
+      <c r="O26" s="8">
+        <v>13.1</v>
       </c>
       <c r="P26" s="9">
-        <v>8.64</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="Q26" s="10">
-        <v>-13.4</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2569,39 +2577,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>0.872</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="I27" s="8">
-        <v>7.75</v>
+        <v>3.99</v>
       </c>
       <c r="J27" s="10">
-        <v>-17.600000000000001</v>
+        <v>-9.36</v>
       </c>
       <c r="K27" s="9">
-        <v>7.74</v>
+        <v>8.64</v>
       </c>
       <c r="L27" s="10">
-        <v>-13.9</v>
+        <v>-13.4</v>
       </c>
       <c r="M27" s="9">
-        <v>0.872</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="N27" s="8">
-        <v>7.75</v>
+        <v>3.99</v>
       </c>
       <c r="O27" s="10">
-        <v>-17.600000000000001</v>
+        <v>-9.36</v>
       </c>
       <c r="P27" s="9">
-        <v>7.74</v>
+        <v>8.64</v>
       </c>
       <c r="Q27" s="10">
-        <v>-13.9</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2622,39 +2630,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>0.80900000000000005</v>
-      </c>
-      <c r="I28" s="10">
-        <v>-20</v>
+        <v>0.872</v>
+      </c>
+      <c r="I28" s="8">
+        <v>7.75</v>
       </c>
       <c r="J28" s="10">
-        <v>-6.35</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="K28" s="9">
-        <v>6.86</v>
+        <v>7.74</v>
       </c>
       <c r="L28" s="10">
-        <v>-13.4</v>
+        <v>-13.9</v>
       </c>
       <c r="M28" s="9">
-        <v>0.80900000000000005</v>
-      </c>
-      <c r="N28" s="10">
-        <v>-20</v>
+        <v>0.872</v>
+      </c>
+      <c r="N28" s="8">
+        <v>7.75</v>
       </c>
       <c r="O28" s="10">
-        <v>-6.35</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="P28" s="9">
-        <v>6.86</v>
+        <v>7.74</v>
       </c>
       <c r="Q28" s="10">
-        <v>-13.4</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2675,39 +2683,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="I29" s="8">
-        <v>12.5</v>
+        <v>0.80900000000000005</v>
+      </c>
+      <c r="I29" s="10">
+        <v>-20</v>
       </c>
       <c r="J29" s="10">
-        <v>-7.17</v>
+        <v>-6.35</v>
       </c>
       <c r="K29" s="9">
-        <v>6.06</v>
+        <v>6.86</v>
       </c>
       <c r="L29" s="10">
-        <v>-14.2</v>
+        <v>-13.4</v>
       </c>
       <c r="M29" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="N29" s="8">
-        <v>12.5</v>
+        <v>0.80900000000000005</v>
+      </c>
+      <c r="N29" s="10">
+        <v>-20</v>
       </c>
       <c r="O29" s="10">
-        <v>-7.17</v>
+        <v>-6.35</v>
       </c>
       <c r="P29" s="9">
-        <v>6.06</v>
+        <v>6.86</v>
       </c>
       <c r="Q29" s="10">
-        <v>-14.2</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2728,39 +2736,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>0.89900000000000002</v>
+        <v>1.01</v>
       </c>
       <c r="I30" s="8">
-        <v>12.2</v>
-      </c>
-      <c r="J30" s="8">
-        <v>11.7</v>
+        <v>12.5</v>
+      </c>
+      <c r="J30" s="10">
+        <v>-7.17</v>
       </c>
       <c r="K30" s="9">
-        <v>5.04</v>
+        <v>6.06</v>
       </c>
       <c r="L30" s="10">
-        <v>-15.5</v>
+        <v>-14.2</v>
       </c>
       <c r="M30" s="9">
-        <v>0.89900000000000002</v>
+        <v>1.01</v>
       </c>
       <c r="N30" s="8">
-        <v>12.2</v>
-      </c>
-      <c r="O30" s="8">
-        <v>11.7</v>
+        <v>12.5</v>
+      </c>
+      <c r="O30" s="10">
+        <v>-7.17</v>
       </c>
       <c r="P30" s="9">
-        <v>5.04</v>
+        <v>6.06</v>
       </c>
       <c r="Q30" s="10">
-        <v>-15.5</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2781,39 +2789,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="9">
-        <v>0.80100000000000005</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="I31" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="J31" s="10">
-        <v>-25.3</v>
+        <v>12.2</v>
+      </c>
+      <c r="J31" s="8">
+        <v>11.7</v>
       </c>
       <c r="K31" s="9">
-        <v>4.1500000000000004</v>
+        <v>5.04</v>
       </c>
       <c r="L31" s="10">
-        <v>-19.8</v>
+        <v>-15.5</v>
       </c>
       <c r="M31" s="9">
-        <v>0.80100000000000005</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="N31" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="O31" s="10">
-        <v>-25.3</v>
+        <v>12.2</v>
+      </c>
+      <c r="O31" s="8">
+        <v>11.7</v>
       </c>
       <c r="P31" s="9">
-        <v>4.1500000000000004</v>
+        <v>5.04</v>
       </c>
       <c r="Q31" s="10">
-        <v>-19.8</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2834,39 +2842,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="9">
-        <v>0.79100000000000004</v>
-      </c>
-      <c r="I32" s="10">
-        <v>-7.87</v>
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="I32" s="8">
+        <v>1.2</v>
       </c>
       <c r="J32" s="10">
-        <v>-26.9</v>
+        <v>-25.3</v>
       </c>
       <c r="K32" s="9">
-        <v>3.34</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="L32" s="10">
-        <v>-18.3</v>
+        <v>-19.8</v>
       </c>
       <c r="M32" s="9">
-        <v>0.79100000000000004</v>
-      </c>
-      <c r="N32" s="10">
-        <v>-7.87</v>
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="N32" s="8">
+        <v>1.2</v>
       </c>
       <c r="O32" s="10">
-        <v>-26.9</v>
+        <v>-25.3</v>
       </c>
       <c r="P32" s="9">
-        <v>3.34</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q32" s="10">
-        <v>-18.3</v>
+        <v>-19.8</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2887,39 +2895,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="I33" s="8">
-        <v>12.2</v>
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="I33" s="10">
+        <v>-7.87</v>
       </c>
       <c r="J33" s="10">
-        <v>-18.899999999999999</v>
+        <v>-26.9</v>
       </c>
       <c r="K33" s="9">
-        <v>2.5499999999999998</v>
+        <v>3.34</v>
       </c>
       <c r="L33" s="10">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="M33" s="9">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="N33" s="8">
-        <v>12.2</v>
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="N33" s="10">
+        <v>-7.87</v>
       </c>
       <c r="O33" s="10">
-        <v>-18.899999999999999</v>
+        <v>-26.9</v>
       </c>
       <c r="P33" s="9">
-        <v>2.5499999999999998</v>
+        <v>3.34</v>
       </c>
       <c r="Q33" s="10">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2940,39 +2948,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="I34" s="10">
-        <v>-17.600000000000001</v>
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="I34" s="8">
+        <v>12.2</v>
       </c>
       <c r="J34" s="10">
-        <v>-11.6</v>
+        <v>-18.899999999999999</v>
       </c>
       <c r="K34" s="9">
-        <v>1.69</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="L34" s="10">
-        <v>-13.2</v>
+        <v>-15.2</v>
       </c>
       <c r="M34" s="9">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="N34" s="10">
-        <v>-17.600000000000001</v>
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="N34" s="8">
+        <v>12.2</v>
       </c>
       <c r="O34" s="10">
-        <v>-11.6</v>
+        <v>-18.899999999999999</v>
       </c>
       <c r="P34" s="9">
-        <v>1.69</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q34" s="10">
-        <v>-13.2</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2993,39 +3001,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>17</v>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="I35" s="10">
+        <v>-17.600000000000001</v>
       </c>
       <c r="J35" s="10">
-        <v>-14.4</v>
+        <v>-11.6</v>
       </c>
       <c r="K35" s="9">
-        <v>0.92900000000000005</v>
+        <v>1.69</v>
       </c>
       <c r="L35" s="10">
-        <v>-14.4</v>
+        <v>-13.2</v>
       </c>
       <c r="M35" s="9">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>17</v>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="N35" s="10">
+        <v>-17.600000000000001</v>
       </c>
       <c r="O35" s="10">
-        <v>-14.4</v>
+        <v>-11.6</v>
       </c>
       <c r="P35" s="9">
-        <v>0.92900000000000005</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" s="10">
-        <v>-14.4</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>41913</v>
+        <v>42005</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3046,39 +3054,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>1</v>
-      </c>
-      <c r="I36" s="10">
-        <v>-5.49</v>
-      </c>
-      <c r="J36" s="8">
-        <v>4.5999999999999996</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="10">
+        <v>-14.4</v>
       </c>
       <c r="K36" s="9">
-        <v>9.98</v>
-      </c>
-      <c r="L36" s="8">
-        <v>5.48</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="L36" s="10">
+        <v>-14.4</v>
       </c>
       <c r="M36" s="9">
-        <v>1</v>
-      </c>
-      <c r="N36" s="10">
-        <v>-5.49</v>
-      </c>
-      <c r="O36" s="8">
-        <v>4.5999999999999996</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O36" s="10">
+        <v>-14.4</v>
       </c>
       <c r="P36" s="9">
-        <v>9.98</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>5.48</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>-14.4</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3099,39 +3107,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="I37" s="8">
-        <v>22.5</v>
+        <v>1</v>
+      </c>
+      <c r="I37" s="10">
+        <v>-5.49</v>
       </c>
       <c r="J37" s="8">
-        <v>24.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K37" s="9">
-        <v>8.98</v>
+        <v>9.98</v>
       </c>
       <c r="L37" s="8">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="M37" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="N37" s="8">
-        <v>22.5</v>
+        <v>1</v>
+      </c>
+      <c r="N37" s="10">
+        <v>-5.49</v>
       </c>
       <c r="O37" s="8">
-        <v>24.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P37" s="9">
-        <v>8.98</v>
+        <v>9.98</v>
       </c>
       <c r="Q37" s="8">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>41852</v>
+        <v>41883</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3152,39 +3160,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="I38" s="10">
-        <v>-20.7</v>
-      </c>
-      <c r="J38" s="10">
-        <v>-16.8</v>
+        <v>1.06</v>
+      </c>
+      <c r="I38" s="8">
+        <v>22.5</v>
+      </c>
+      <c r="J38" s="8">
+        <v>24.5</v>
       </c>
       <c r="K38" s="9">
-        <v>7.92</v>
+        <v>8.98</v>
       </c>
       <c r="L38" s="8">
-        <v>3.49</v>
+        <v>5.58</v>
       </c>
       <c r="M38" s="9">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="N38" s="10">
-        <v>-20.7</v>
-      </c>
-      <c r="O38" s="10">
-        <v>-16.8</v>
+        <v>1.06</v>
+      </c>
+      <c r="N38" s="8">
+        <v>22.5</v>
+      </c>
+      <c r="O38" s="8">
+        <v>24.5</v>
       </c>
       <c r="P38" s="9">
-        <v>7.92</v>
+        <v>8.98</v>
       </c>
       <c r="Q38" s="8">
-        <v>3.49</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3205,39 +3213,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I39" s="8">
-        <v>35.4</v>
-      </c>
-      <c r="J39" s="8">
-        <v>10.7</v>
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="I39" s="10">
+        <v>-20.7</v>
+      </c>
+      <c r="J39" s="10">
+        <v>-16.8</v>
       </c>
       <c r="K39" s="9">
-        <v>7.06</v>
+        <v>7.92</v>
       </c>
       <c r="L39" s="8">
-        <v>6.67</v>
+        <v>3.49</v>
       </c>
       <c r="M39" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N39" s="8">
-        <v>35.4</v>
-      </c>
-      <c r="O39" s="8">
-        <v>10.7</v>
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="N39" s="10">
+        <v>-20.7</v>
+      </c>
+      <c r="O39" s="10">
+        <v>-16.8</v>
       </c>
       <c r="P39" s="9">
-        <v>7.06</v>
+        <v>7.92</v>
       </c>
       <c r="Q39" s="8">
-        <v>6.67</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3258,39 +3266,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="I40" s="10">
-        <v>-25</v>
-      </c>
-      <c r="J40" s="10">
-        <v>-16.7</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I40" s="8">
+        <v>35.4</v>
+      </c>
+      <c r="J40" s="8">
+        <v>10.7</v>
       </c>
       <c r="K40" s="9">
-        <v>5.97</v>
+        <v>7.06</v>
       </c>
       <c r="L40" s="8">
-        <v>5.96</v>
+        <v>6.67</v>
       </c>
       <c r="M40" s="9">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="N40" s="10">
-        <v>-25</v>
-      </c>
-      <c r="O40" s="10">
-        <v>-16.7</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N40" s="8">
+        <v>35.4</v>
+      </c>
+      <c r="O40" s="8">
+        <v>10.7</v>
       </c>
       <c r="P40" s="9">
-        <v>5.97</v>
+        <v>7.06</v>
       </c>
       <c r="Q40" s="8">
-        <v>5.96</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3311,39 +3319,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>1.07</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="I41" s="10">
-        <v>-0.93</v>
+        <v>-25</v>
       </c>
       <c r="J41" s="10">
-        <v>-1.6</v>
+        <v>-16.7</v>
       </c>
       <c r="K41" s="9">
-        <v>5.17</v>
+        <v>5.97</v>
       </c>
       <c r="L41" s="8">
-        <v>10.6</v>
+        <v>5.96</v>
       </c>
       <c r="M41" s="9">
-        <v>1.07</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="N41" s="10">
-        <v>-0.93</v>
+        <v>-25</v>
       </c>
       <c r="O41" s="10">
-        <v>-1.6</v>
+        <v>-16.7</v>
       </c>
       <c r="P41" s="9">
-        <v>5.17</v>
+        <v>5.97</v>
       </c>
       <c r="Q41" s="8">
-        <v>10.6</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3364,39 +3372,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="I42" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="J42" s="8">
-        <v>10.4</v>
+        <v>1.07</v>
+      </c>
+      <c r="I42" s="10">
+        <v>-0.93</v>
+      </c>
+      <c r="J42" s="10">
+        <v>-1.6</v>
       </c>
       <c r="K42" s="9">
-        <v>4.09</v>
+        <v>5.17</v>
       </c>
       <c r="L42" s="8">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="M42" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="N42" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="O42" s="8">
-        <v>10.4</v>
+        <v>1.07</v>
+      </c>
+      <c r="N42" s="10">
+        <v>-0.93</v>
+      </c>
+      <c r="O42" s="10">
+        <v>-1.6</v>
       </c>
       <c r="P42" s="9">
-        <v>4.09</v>
+        <v>5.17</v>
       </c>
       <c r="Q42" s="8">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3417,39 +3425,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I43" s="8">
-        <v>22.3</v>
+        <v>2.16</v>
       </c>
       <c r="J43" s="8">
-        <v>14.1</v>
+        <v>10.4</v>
       </c>
       <c r="K43" s="9">
-        <v>3.01</v>
+        <v>4.09</v>
       </c>
       <c r="L43" s="8">
-        <v>15.9</v>
+        <v>14.4</v>
       </c>
       <c r="M43" s="9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N43" s="8">
-        <v>22.3</v>
+        <v>2.16</v>
       </c>
       <c r="O43" s="8">
-        <v>14.1</v>
+        <v>10.4</v>
       </c>
       <c r="P43" s="9">
-        <v>3.01</v>
+        <v>4.09</v>
       </c>
       <c r="Q43" s="8">
-        <v>15.9</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3470,39 +3478,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="I44" s="10">
-        <v>-20.2</v>
+        <v>1.06</v>
+      </c>
+      <c r="I44" s="8">
+        <v>22.3</v>
       </c>
       <c r="J44" s="8">
-        <v>2.04</v>
+        <v>14.1</v>
       </c>
       <c r="K44" s="9">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="L44" s="8">
-        <v>16.899999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="M44" s="9">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="N44" s="10">
-        <v>-20.2</v>
+        <v>1.06</v>
+      </c>
+      <c r="N44" s="8">
+        <v>22.3</v>
       </c>
       <c r="O44" s="8">
-        <v>2.04</v>
+        <v>14.1</v>
       </c>
       <c r="P44" s="9">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q44" s="8">
-        <v>16.899999999999999</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3523,39 +3531,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I45" s="8">
-        <v>9.5399999999999991</v>
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="I45" s="10">
+        <v>-20.2</v>
       </c>
       <c r="J45" s="8">
-        <v>32.200000000000003</v>
+        <v>2.04</v>
       </c>
       <c r="K45" s="9">
-        <v>1.0900000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="L45" s="8">
-        <v>32.200000000000003</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M45" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N45" s="8">
-        <v>9.5399999999999991</v>
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="N45" s="10">
+        <v>-20.2</v>
       </c>
       <c r="O45" s="8">
-        <v>32.200000000000003</v>
+        <v>2.04</v>
       </c>
       <c r="P45" s="9">
-        <v>1.0900000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" s="8">
-        <v>32.200000000000003</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3576,39 +3584,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>0.99099999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I46" s="8">
-        <v>6.41</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="J46" s="8">
-        <v>33.200000000000003</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="K46" s="9">
-        <v>11.39</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="L46" s="8">
-        <v>31.6</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="M46" s="9">
-        <v>0.99099999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N46" s="8">
-        <v>6.41</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="O46" s="8">
-        <v>33.200000000000003</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="P46" s="9">
-        <v>11.39</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="Q46" s="8">
-        <v>31.6</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3629,39 +3637,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>0.93200000000000005</v>
-      </c>
-      <c r="I47" s="10">
-        <v>-2.5499999999999998</v>
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="I47" s="8">
+        <v>6.41</v>
       </c>
       <c r="J47" s="8">
-        <v>27.7</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="K47" s="9">
-        <v>10.39</v>
+        <v>11.39</v>
       </c>
       <c r="L47" s="8">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="M47" s="9">
-        <v>0.93200000000000005</v>
-      </c>
-      <c r="N47" s="10">
-        <v>-2.5499999999999998</v>
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="N47" s="8">
+        <v>6.41</v>
       </c>
       <c r="O47" s="8">
-        <v>27.7</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="P47" s="9">
-        <v>10.39</v>
+        <v>11.39</v>
       </c>
       <c r="Q47" s="8">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3682,39 +3690,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="I48" s="8">
-        <v>12.4</v>
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="I48" s="10">
+        <v>-2.5499999999999998</v>
       </c>
       <c r="J48" s="8">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="K48" s="9">
-        <v>9.4600000000000009</v>
+        <v>10.39</v>
       </c>
       <c r="L48" s="8">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
       <c r="M48" s="9">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="N48" s="8">
-        <v>12.4</v>
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="N48" s="10">
+        <v>-2.5499999999999998</v>
       </c>
       <c r="O48" s="8">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="P48" s="9">
-        <v>9.4600000000000009</v>
+        <v>10.39</v>
       </c>
       <c r="Q48" s="8">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3735,39 +3743,39 @@
         <v>17</v>
       </c>
       <c r="H49" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="I49" s="10">
-        <v>-18.100000000000001</v>
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="I49" s="8">
+        <v>12.4</v>
       </c>
       <c r="J49" s="8">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="K49" s="9">
-        <v>8.51</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="L49" s="8">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="M49" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="N49" s="10">
-        <v>-18.100000000000001</v>
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="N49" s="8">
+        <v>12.4</v>
       </c>
       <c r="O49" s="8">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="P49" s="9">
-        <v>8.51</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="Q49" s="8">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3788,39 +3796,39 @@
         <v>17</v>
       </c>
       <c r="H50" s="9">
-        <v>1.04</v>
-      </c>
-      <c r="I50" s="8">
-        <v>5.52</v>
+        <v>0.85</v>
+      </c>
+      <c r="I50" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="J50" s="8">
-        <v>47.1</v>
+        <v>28.6</v>
       </c>
       <c r="K50" s="9">
-        <v>7.66</v>
+        <v>8.51</v>
       </c>
       <c r="L50" s="8">
-        <v>32.799999999999997</v>
+        <v>32.4</v>
       </c>
       <c r="M50" s="9">
-        <v>1.04</v>
-      </c>
-      <c r="N50" s="8">
-        <v>5.52</v>
+        <v>0.85</v>
+      </c>
+      <c r="N50" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="O50" s="8">
-        <v>47.1</v>
+        <v>28.6</v>
       </c>
       <c r="P50" s="9">
-        <v>7.66</v>
+        <v>8.51</v>
       </c>
       <c r="Q50" s="8">
-        <v>32.799999999999997</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3841,39 +3849,39 @@
         <v>17</v>
       </c>
       <c r="H51" s="9">
-        <v>0.98399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I51" s="8">
-        <v>1.88</v>
+        <v>5.52</v>
       </c>
       <c r="J51" s="8">
-        <v>67.2</v>
+        <v>47.1</v>
       </c>
       <c r="K51" s="9">
-        <v>6.62</v>
+        <v>7.66</v>
       </c>
       <c r="L51" s="8">
-        <v>30.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="M51" s="9">
-        <v>0.98399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="N51" s="8">
-        <v>1.88</v>
+        <v>5.52</v>
       </c>
       <c r="O51" s="8">
-        <v>67.2</v>
+        <v>47.1</v>
       </c>
       <c r="P51" s="9">
-        <v>6.62</v>
+        <v>7.66</v>
       </c>
       <c r="Q51" s="8">
-        <v>30.8</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3894,39 +3902,39 @@
         <v>17</v>
       </c>
       <c r="H52" s="9">
-        <v>0.96599999999999997</v>
-      </c>
-      <c r="I52" s="10">
-        <v>-11.4</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="I52" s="8">
+        <v>1.88</v>
       </c>
       <c r="J52" s="8">
-        <v>65</v>
+        <v>67.2</v>
       </c>
       <c r="K52" s="9">
-        <v>5.64</v>
+        <v>6.62</v>
       </c>
       <c r="L52" s="8">
-        <v>26.1</v>
+        <v>30.8</v>
       </c>
       <c r="M52" s="9">
-        <v>0.96599999999999997</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>17</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="N52" s="8">
+        <v>1.88</v>
       </c>
       <c r="O52" s="8">
-        <v>65</v>
+        <v>67.2</v>
       </c>
       <c r="P52" s="9">
-        <v>5.64</v>
+        <v>6.62</v>
       </c>
       <c r="Q52" s="8">
-        <v>26.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3947,39 +3955,39 @@
         <v>17</v>
       </c>
       <c r="H53" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I53" s="8">
-        <v>11.1</v>
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="I53" s="10">
+        <v>-11.4</v>
       </c>
       <c r="J53" s="8">
-        <v>22.6</v>
+        <v>65</v>
       </c>
       <c r="K53" s="9">
-        <v>4.67</v>
+        <v>5.64</v>
       </c>
       <c r="L53" s="8">
-        <v>20.2</v>
+        <v>26.1</v>
       </c>
       <c r="M53" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N53" s="8">
-        <v>11.1</v>
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O53" s="8">
-        <v>22.6</v>
+        <v>65</v>
       </c>
       <c r="P53" s="9">
-        <v>4.67</v>
+        <v>5.64</v>
       </c>
       <c r="Q53" s="8">
-        <v>20.2</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4000,39 +4008,39 @@
         <v>17</v>
       </c>
       <c r="H54" s="9">
-        <v>0.98099999999999998</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I54" s="8">
-        <v>5.62</v>
+        <v>11.1</v>
       </c>
       <c r="J54" s="8">
-        <v>18.100000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="K54" s="9">
-        <v>3.58</v>
+        <v>4.67</v>
       </c>
       <c r="L54" s="8">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
       <c r="M54" s="9">
-        <v>0.98099999999999998</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N54" s="8">
-        <v>5.62</v>
+        <v>11.1</v>
       </c>
       <c r="O54" s="8">
-        <v>18.100000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="P54" s="9">
-        <v>3.58</v>
+        <v>4.67</v>
       </c>
       <c r="Q54" s="8">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4053,39 +4061,39 @@
         <v>17</v>
       </c>
       <c r="H55" s="9">
-        <v>0.92900000000000005</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="I55" s="8">
-        <v>9.3699999999999992</v>
+        <v>5.62</v>
       </c>
       <c r="J55" s="8">
-        <v>23.6</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="K55" s="9">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="L55" s="8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M55" s="9">
-        <v>0.92900000000000005</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="N55" s="8">
-        <v>9.3699999999999992</v>
+        <v>5.62</v>
       </c>
       <c r="O55" s="8">
-        <v>23.6</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="P55" s="9">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="Q55" s="8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4106,39 +4114,39 @@
         <v>17</v>
       </c>
       <c r="H56" s="9">
-        <v>0.84899999999999998</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="I56" s="8">
-        <v>3.37</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="J56" s="8">
-        <v>27.3</v>
+        <v>23.6</v>
       </c>
       <c r="K56" s="9">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="L56" s="8">
-        <v>18.100000000000001</v>
+        <v>20</v>
       </c>
       <c r="M56" s="9">
-        <v>0.84899999999999998</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="N56" s="8">
-        <v>3.37</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="O56" s="8">
-        <v>27.3</v>
+        <v>23.6</v>
       </c>
       <c r="P56" s="9">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q56" s="8">
-        <v>18.100000000000001</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4159,39 +4167,39 @@
         <v>17</v>
       </c>
       <c r="H57" s="9">
-        <v>0.82099999999999995</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="I57" s="8">
-        <v>10.4</v>
+        <v>3.37</v>
       </c>
       <c r="J57" s="8">
-        <v>9.9</v>
+        <v>27.3</v>
       </c>
       <c r="K57" s="9">
-        <v>0.82099999999999995</v>
+        <v>1.67</v>
       </c>
       <c r="L57" s="8">
-        <v>9.9</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="M57" s="9">
-        <v>0.82099999999999995</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="N57" s="8">
-        <v>10.4</v>
+        <v>3.37</v>
       </c>
       <c r="O57" s="8">
-        <v>9.9</v>
+        <v>27.3</v>
       </c>
       <c r="P57" s="9">
-        <v>0.82099999999999995</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" s="8">
-        <v>9.9</v>
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4212,39 +4220,39 @@
         <v>17</v>
       </c>
       <c r="H58" s="9">
-        <v>0.74399999999999999</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="I58" s="8">
-        <v>2.0099999999999998</v>
+        <v>10.4</v>
       </c>
       <c r="J58" s="8">
-        <v>9.0299999999999994</v>
+        <v>9.9</v>
       </c>
       <c r="K58" s="9">
-        <v>8.65</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="L58" s="8">
-        <v>3.52</v>
-      </c>
-      <c r="M58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q58" s="9" t="s">
-        <v>17</v>
+        <v>9.9</v>
+      </c>
+      <c r="M58" s="9">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="N58" s="8">
+        <v>10.4</v>
+      </c>
+      <c r="O58" s="8">
+        <v>9.9</v>
+      </c>
+      <c r="P58" s="9">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>9.9</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4265,19 +4273,19 @@
         <v>17</v>
       </c>
       <c r="H59" s="9">
-        <v>0.72899999999999998</v>
-      </c>
-      <c r="I59" s="10">
-        <v>-2.64</v>
-      </c>
-      <c r="J59" s="10">
-        <v>-4.7300000000000004</v>
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="I59" s="8">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="J59" s="8">
+        <v>9.0299999999999994</v>
       </c>
       <c r="K59" s="9">
-        <v>7.9</v>
+        <v>8.65</v>
       </c>
       <c r="L59" s="8">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="M59" s="9" t="s">
         <v>17</v>
@@ -4297,7 +4305,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4318,19 +4326,19 @@
         <v>17</v>
       </c>
       <c r="H60" s="9">
-        <v>0.749</v>
-      </c>
-      <c r="I60" s="8">
-        <v>13.3</v>
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="I60" s="10">
+        <v>-2.64</v>
       </c>
       <c r="J60" s="10">
-        <v>-16.8</v>
+        <v>-4.7300000000000004</v>
       </c>
       <c r="K60" s="9">
-        <v>7.17</v>
+        <v>7.9</v>
       </c>
       <c r="L60" s="8">
-        <v>3.89</v>
+        <v>3.03</v>
       </c>
       <c r="M60" s="9" t="s">
         <v>17</v>
@@ -4350,7 +4358,7 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4371,19 +4379,19 @@
         <v>17</v>
       </c>
       <c r="H61" s="9">
-        <v>0.66100000000000003</v>
-      </c>
-      <c r="I61" s="10">
-        <v>-6.32</v>
+        <v>0.749</v>
+      </c>
+      <c r="I61" s="8">
+        <v>13.3</v>
       </c>
       <c r="J61" s="10">
-        <v>-11</v>
+        <v>-16.8</v>
       </c>
       <c r="K61" s="9">
-        <v>6.43</v>
+        <v>7.17</v>
       </c>
       <c r="L61" s="8">
-        <v>7</v>
+        <v>3.89</v>
       </c>
       <c r="M61" s="9" t="s">
         <v>17</v>
@@ -4403,7 +4411,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4424,19 +4432,19 @@
         <v>17</v>
       </c>
       <c r="H62" s="9">
-        <v>0.70599999999999996</v>
-      </c>
-      <c r="I62" s="8">
-        <v>20</v>
-      </c>
-      <c r="J62" s="8">
-        <v>9.4700000000000006</v>
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="I62" s="10">
+        <v>-6.32</v>
+      </c>
+      <c r="J62" s="10">
+        <v>-11</v>
       </c>
       <c r="K62" s="9">
-        <v>5.76</v>
+        <v>6.43</v>
       </c>
       <c r="L62" s="8">
-        <v>9.5500000000000007</v>
+        <v>7</v>
       </c>
       <c r="M62" s="9" t="s">
         <v>17</v>
@@ -4456,7 +4464,7 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4477,19 +4485,19 @@
         <v>17</v>
       </c>
       <c r="H63" s="9">
-        <v>0.58799999999999997</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="I63" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="J63" s="10">
-        <v>-16.7</v>
+        <v>20</v>
+      </c>
+      <c r="J63" s="8">
+        <v>9.4700000000000006</v>
       </c>
       <c r="K63" s="9">
-        <v>5.0599999999999996</v>
+        <v>5.76</v>
       </c>
       <c r="L63" s="8">
-        <v>9.56</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="M63" s="9" t="s">
         <v>17</v>
@@ -4509,7 +4517,7 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4530,19 +4538,19 @@
         <v>17</v>
       </c>
       <c r="H64" s="9">
-        <v>0.58499999999999996</v>
-      </c>
-      <c r="I64" s="10">
-        <v>-34.200000000000003</v>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I64" s="8">
+        <v>0.52</v>
       </c>
       <c r="J64" s="10">
-        <v>-18.100000000000001</v>
+        <v>-16.7</v>
       </c>
       <c r="K64" s="9">
-        <v>4.47</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="L64" s="8">
-        <v>14.3</v>
+        <v>9.56</v>
       </c>
       <c r="M64" s="9" t="s">
         <v>17</v>
@@ -4562,7 +4570,7 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>41030</v>
+        <v>41061</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4583,19 +4591,19 @@
         <v>17</v>
       </c>
       <c r="H65" s="9">
-        <v>0.88900000000000001</v>
-      </c>
-      <c r="I65" s="8">
-        <v>7.02</v>
-      </c>
-      <c r="J65" s="8">
-        <v>33.799999999999997</v>
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="I65" s="10">
+        <v>-34.200000000000003</v>
+      </c>
+      <c r="J65" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="K65" s="9">
-        <v>3.89</v>
+        <v>4.47</v>
       </c>
       <c r="L65" s="8">
-        <v>21.6</v>
+        <v>14.3</v>
       </c>
       <c r="M65" s="9" t="s">
         <v>17</v>
@@ -4615,7 +4623,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>41000</v>
+        <v>41030</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4636,19 +4644,19 @@
         <v>17</v>
       </c>
       <c r="H66" s="9">
-        <v>0.83099999999999996</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="I66" s="8">
-        <v>10.5</v>
+        <v>7.02</v>
       </c>
       <c r="J66" s="8">
-        <v>22.6</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="K66" s="9">
-        <v>3</v>
+        <v>3.89</v>
       </c>
       <c r="L66" s="8">
-        <v>18.3</v>
+        <v>21.6</v>
       </c>
       <c r="M66" s="9" t="s">
         <v>17</v>
@@ -4668,7 +4676,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>40969</v>
+        <v>41000</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4689,19 +4697,19 @@
         <v>17</v>
       </c>
       <c r="H67" s="9">
-        <v>0.751</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="I67" s="8">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="J67" s="8">
-        <v>8.85</v>
+        <v>22.6</v>
       </c>
       <c r="K67" s="9">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="L67" s="8">
-        <v>16.8</v>
+        <v>18.3</v>
       </c>
       <c r="M67" s="9" t="s">
         <v>17</v>
@@ -4721,7 +4729,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>40940</v>
+        <v>40969</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4742,19 +4750,19 @@
         <v>17</v>
       </c>
       <c r="H68" s="9">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="I68" s="10">
-        <v>-10.7</v>
+        <v>0.751</v>
+      </c>
+      <c r="I68" s="8">
+        <v>12.7</v>
       </c>
       <c r="J68" s="8">
-        <v>36.5</v>
+        <v>8.85</v>
       </c>
       <c r="K68" s="9">
-        <v>1.41</v>
+        <v>2.17</v>
       </c>
       <c r="L68" s="8">
-        <v>21.5</v>
+        <v>16.8</v>
       </c>
       <c r="M68" s="9" t="s">
         <v>17</v>
@@ -4774,7 +4782,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>40909</v>
+        <v>40940</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4795,19 +4803,19 @@
         <v>17</v>
       </c>
       <c r="H69" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="I69" s="8">
-        <v>9.48</v>
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="I69" s="10">
+        <v>-10.7</v>
       </c>
       <c r="J69" s="8">
-        <v>10.6</v>
+        <v>36.5</v>
       </c>
       <c r="K69" s="9">
-        <v>0.747</v>
+        <v>1.41</v>
       </c>
       <c r="L69" s="8">
-        <v>10.6</v>
+        <v>21.5</v>
       </c>
       <c r="M69" s="9" t="s">
         <v>17</v>
@@ -4827,40 +4835,40 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>40878</v>
-      </c>
-      <c r="B70" s="7">
-        <v>5.18</v>
-      </c>
-      <c r="C70" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="D70" s="7">
-        <v>5.43</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.68</v>
-      </c>
-      <c r="F70" s="10">
-        <v>-1.98</v>
-      </c>
-      <c r="G70" s="10">
-        <v>-38.22</v>
+        <v>40909</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="H70" s="9">
-        <v>0.68200000000000005</v>
-      </c>
-      <c r="I70" s="10">
-        <v>-10.9</v>
+        <v>0.747</v>
+      </c>
+      <c r="I70" s="8">
+        <v>9.48</v>
       </c>
       <c r="J70" s="8">
-        <v>57.8</v>
+        <v>10.6</v>
       </c>
       <c r="K70" s="9">
-        <v>8.35</v>
+        <v>0.747</v>
       </c>
       <c r="L70" s="8">
-        <v>46.6</v>
+        <v>10.6</v>
       </c>
       <c r="M70" s="9" t="s">
         <v>17</v>
@@ -4880,40 +4888,40 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>40848</v>
+        <v>40878</v>
       </c>
       <c r="B71" s="7">
-        <v>5.36</v>
+        <v>5.18</v>
       </c>
       <c r="C71" s="7">
-        <v>5.18</v>
+        <v>3.2</v>
       </c>
       <c r="D71" s="7">
-        <v>7.8</v>
+        <v>5.43</v>
       </c>
       <c r="E71" s="7">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="F71" s="10">
-        <v>-0.18</v>
+        <v>-1.98</v>
       </c>
       <c r="G71" s="10">
-        <v>-3.36</v>
+        <v>-38.22</v>
       </c>
       <c r="H71" s="9">
-        <v>0.76600000000000001</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="I71" s="10">
-        <v>-15</v>
+        <v>-10.9</v>
       </c>
       <c r="J71" s="8">
-        <v>60.2</v>
+        <v>57.8</v>
       </c>
       <c r="K71" s="9">
-        <v>7.67</v>
+        <v>8.35</v>
       </c>
       <c r="L71" s="8">
-        <v>45.7</v>
+        <v>46.6</v>
       </c>
       <c r="M71" s="9" t="s">
         <v>17</v>
@@ -4933,40 +4941,40 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>40817</v>
+        <v>40848</v>
       </c>
       <c r="B72" s="7">
-        <v>5.13</v>
+        <v>5.36</v>
       </c>
       <c r="C72" s="7">
-        <v>5.36</v>
+        <v>5.18</v>
       </c>
       <c r="D72" s="7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="E72" s="7">
-        <v>4.93</v>
-      </c>
-      <c r="F72" s="8">
-        <v>0.23</v>
-      </c>
-      <c r="G72" s="8">
-        <v>4.4800000000000004</v>
+        <v>5</v>
+      </c>
+      <c r="F72" s="10">
+        <v>-0.18</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-3.36</v>
       </c>
       <c r="H72" s="9">
-        <v>0.90100000000000002</v>
-      </c>
-      <c r="I72" s="8">
-        <v>21.2</v>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="I72" s="10">
+        <v>-15</v>
       </c>
       <c r="J72" s="8">
-        <v>107</v>
+        <v>60.2</v>
       </c>
       <c r="K72" s="9">
-        <v>6.91</v>
+        <v>7.67</v>
       </c>
       <c r="L72" s="8">
-        <v>44.2</v>
+        <v>45.7</v>
       </c>
       <c r="M72" s="9" t="s">
         <v>17</v>
@@ -4986,40 +4994,40 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>40787</v>
+        <v>40817</v>
       </c>
       <c r="B73" s="7">
-        <v>9.15</v>
+        <v>5.13</v>
       </c>
       <c r="C73" s="7">
-        <v>5.13</v>
+        <v>5.36</v>
       </c>
       <c r="D73" s="7">
-        <v>9.35</v>
+        <v>7.2</v>
       </c>
       <c r="E73" s="7">
-        <v>3.33</v>
-      </c>
-      <c r="F73" s="10">
-        <v>-4.0199999999999996</v>
-      </c>
-      <c r="G73" s="10">
-        <v>-43.93</v>
+        <v>4.93</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="G73" s="8">
+        <v>4.4800000000000004</v>
       </c>
       <c r="H73" s="9">
-        <v>0.74299999999999999</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="I73" s="8">
-        <v>15.3</v>
+        <v>21.2</v>
       </c>
       <c r="J73" s="8">
-        <v>75.3</v>
+        <v>107</v>
       </c>
       <c r="K73" s="9">
-        <v>6</v>
+        <v>6.91</v>
       </c>
       <c r="L73" s="8">
-        <v>38</v>
+        <v>44.2</v>
       </c>
       <c r="M73" s="9" t="s">
         <v>17</v>
@@ -5039,40 +5047,40 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>40756</v>
+        <v>40787</v>
       </c>
       <c r="B74" s="7">
-        <v>12.3</v>
+        <v>9.15</v>
       </c>
       <c r="C74" s="7">
-        <v>9.15</v>
+        <v>5.13</v>
       </c>
       <c r="D74" s="7">
-        <v>12.35</v>
+        <v>9.35</v>
       </c>
       <c r="E74" s="7">
-        <v>9.15</v>
+        <v>3.33</v>
       </c>
       <c r="F74" s="10">
-        <v>-3.15</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="G74" s="10">
-        <v>-25.61</v>
+        <v>-43.93</v>
       </c>
       <c r="H74" s="9">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="I74" s="10">
-        <v>-8.68</v>
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="I74" s="8">
+        <v>15.3</v>
       </c>
       <c r="J74" s="8">
-        <v>28</v>
+        <v>75.3</v>
       </c>
       <c r="K74" s="9">
-        <v>5.26</v>
+        <v>6</v>
       </c>
       <c r="L74" s="8">
-        <v>33.9</v>
+        <v>38</v>
       </c>
       <c r="M74" s="9" t="s">
         <v>17</v>
@@ -5092,40 +5100,40 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>40725</v>
+        <v>40756</v>
       </c>
       <c r="B75" s="7">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="C75" s="7">
-        <v>12.3</v>
+        <v>9.15</v>
       </c>
       <c r="D75" s="7">
-        <v>13.3</v>
+        <v>12.35</v>
       </c>
       <c r="E75" s="7">
-        <v>12.3</v>
+        <v>9.15</v>
       </c>
       <c r="F75" s="10">
-        <v>-0.6</v>
+        <v>-3.15</v>
       </c>
       <c r="G75" s="10">
-        <v>-4.6500000000000004</v>
+        <v>-25.61</v>
       </c>
       <c r="H75" s="9">
-        <v>0.70599999999999996</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="I75" s="10">
-        <v>-1.23</v>
+        <v>-8.68</v>
       </c>
       <c r="J75" s="8">
-        <v>62.9</v>
+        <v>28</v>
       </c>
       <c r="K75" s="9">
-        <v>4.62</v>
+        <v>5.26</v>
       </c>
       <c r="L75" s="8">
-        <v>34.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="M75" s="9" t="s">
         <v>17</v>
@@ -5145,40 +5153,40 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>40695</v>
+        <v>40725</v>
       </c>
       <c r="B76" s="7">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="C76" s="7">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="D76" s="7">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="E76" s="7">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F76" s="10">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G76" s="10">
-        <v>-1.53</v>
+        <v>-4.6500000000000004</v>
       </c>
       <c r="H76" s="9">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="I76" s="8">
-        <v>7.61</v>
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="I76" s="10">
+        <v>-1.23</v>
       </c>
       <c r="J76" s="8">
-        <v>32.700000000000003</v>
+        <v>62.9</v>
       </c>
       <c r="K76" s="9">
-        <v>3.91</v>
+        <v>4.62</v>
       </c>
       <c r="L76" s="8">
-        <v>30.8</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="M76" s="9" t="s">
         <v>17</v>
@@ -5198,40 +5206,40 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>40664</v>
+        <v>40695</v>
       </c>
       <c r="B77" s="7">
-        <v>13.95</v>
+        <v>13.1</v>
       </c>
       <c r="C77" s="7">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="D77" s="7">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="E77" s="7">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F77" s="10">
-        <v>-0.85</v>
+        <v>-0.2</v>
       </c>
       <c r="G77" s="10">
-        <v>-6.09</v>
+        <v>-1.53</v>
       </c>
       <c r="H77" s="9">
-        <v>0.66400000000000003</v>
-      </c>
-      <c r="I77" s="10">
-        <v>-1.93</v>
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="I77" s="8">
+        <v>7.61</v>
       </c>
       <c r="J77" s="8">
-        <v>26.8</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="K77" s="9">
-        <v>3.2</v>
+        <v>3.91</v>
       </c>
       <c r="L77" s="8">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="M77" s="9" t="s">
         <v>17</v>
@@ -5251,40 +5259,40 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>40634</v>
+        <v>40664</v>
       </c>
       <c r="B78" s="7">
-        <v>14</v>
+        <v>13.95</v>
       </c>
       <c r="C78" s="7">
-        <v>13.95</v>
+        <v>13.1</v>
       </c>
       <c r="D78" s="7">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="E78" s="7">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="F78" s="10">
-        <v>-0.05</v>
+        <v>-0.85</v>
       </c>
       <c r="G78" s="10">
-        <v>-0.36</v>
+        <v>-6.09</v>
       </c>
       <c r="H78" s="9">
-        <v>0.67700000000000005</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="I78" s="10">
-        <v>-1.88</v>
+        <v>-1.93</v>
       </c>
       <c r="J78" s="8">
-        <v>19.399999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="K78" s="9">
-        <v>2.5299999999999998</v>
+        <v>3.2</v>
       </c>
       <c r="L78" s="8">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="M78" s="9" t="s">
         <v>17</v>
@@ -5304,40 +5312,40 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>40603</v>
+        <v>40634</v>
       </c>
       <c r="B79" s="7">
+        <v>14</v>
+      </c>
+      <c r="C79" s="7">
+        <v>13.95</v>
+      </c>
+      <c r="D79" s="7">
         <v>14.5</v>
       </c>
-      <c r="C79" s="7">
-        <v>14</v>
-      </c>
-      <c r="D79" s="7">
-        <v>16.100000000000001</v>
-      </c>
       <c r="E79" s="7">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F79" s="10">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="G79" s="10">
-        <v>-3.45</v>
+        <v>-0.36</v>
       </c>
       <c r="H79" s="9">
-        <v>0.69</v>
-      </c>
-      <c r="I79" s="8">
-        <v>41.2</v>
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="I79" s="10">
+        <v>-1.88</v>
       </c>
       <c r="J79" s="8">
-        <v>50.2</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="K79" s="9">
-        <v>1.85</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="L79" s="8">
-        <v>36.299999999999997</v>
+        <v>31.3</v>
       </c>
       <c r="M79" s="9" t="s">
         <v>17</v>
@@ -5357,40 +5365,40 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>40575</v>
+        <v>40603</v>
       </c>
       <c r="B80" s="7">
-        <v>13.15</v>
+        <v>14.5</v>
       </c>
       <c r="C80" s="7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D80" s="7">
-        <v>16.2</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="E80" s="7">
-        <v>13</v>
-      </c>
-      <c r="F80" s="8">
-        <v>1.35</v>
-      </c>
-      <c r="G80" s="8">
-        <v>10.27</v>
+        <v>13.8</v>
+      </c>
+      <c r="F80" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-3.45</v>
       </c>
       <c r="H80" s="9">
-        <v>0.48899999999999999</v>
-      </c>
-      <c r="I80" s="10">
-        <v>-27.6</v>
+        <v>0.69</v>
+      </c>
+      <c r="I80" s="8">
+        <v>41.2</v>
       </c>
       <c r="J80" s="8">
-        <v>7.87</v>
+        <v>50.2</v>
       </c>
       <c r="K80" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="L80" s="8">
-        <v>29.2</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="M80" s="9" t="s">
         <v>17</v>
@@ -5410,40 +5418,40 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>40544</v>
+        <v>40575</v>
       </c>
       <c r="B81" s="7">
-        <v>15.1</v>
+        <v>13.15</v>
       </c>
       <c r="C81" s="7">
-        <v>13.15</v>
+        <v>14.5</v>
       </c>
       <c r="D81" s="7">
-        <v>13.85</v>
+        <v>16.2</v>
       </c>
       <c r="E81" s="7">
         <v>13</v>
       </c>
-      <c r="F81" s="10">
-        <v>-1.95</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-12.91</v>
+      <c r="F81" s="8">
+        <v>1.35</v>
+      </c>
+      <c r="G81" s="8">
+        <v>10.27</v>
       </c>
       <c r="H81" s="9">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="I81" s="8">
-        <v>56.1</v>
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="I81" s="10">
+        <v>-27.6</v>
       </c>
       <c r="J81" s="8">
-        <v>50.8</v>
+        <v>7.87</v>
       </c>
       <c r="K81" s="9">
-        <v>0.67500000000000004</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="L81" s="8">
-        <v>50.8</v>
+        <v>29.2</v>
       </c>
       <c r="M81" s="9" t="s">
         <v>17</v>
@@ -5463,40 +5471,40 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>40513</v>
+        <v>40544</v>
       </c>
       <c r="B82" s="7">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="C82" s="7">
-        <v>15.1</v>
+        <v>13.15</v>
       </c>
       <c r="D82" s="7">
-        <v>15.1</v>
+        <v>13.85</v>
       </c>
       <c r="E82" s="7">
-        <v>12.7</v>
-      </c>
-      <c r="F82" s="8">
-        <v>2</v>
-      </c>
-      <c r="G82" s="8">
-        <v>15.27</v>
+        <v>13</v>
+      </c>
+      <c r="F82" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-12.91</v>
       </c>
       <c r="H82" s="9">
-        <v>0.433</v>
-      </c>
-      <c r="I82" s="10">
-        <v>-9.4700000000000006</v>
-      </c>
-      <c r="J82" s="10">
-        <v>-51.9</v>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="I82" s="8">
+        <v>56.1</v>
+      </c>
+      <c r="J82" s="8">
+        <v>50.8</v>
       </c>
       <c r="K82" s="9">
-        <v>5.7</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="L82" s="8">
-        <v>7.35</v>
+        <v>50.8</v>
       </c>
       <c r="M82" s="9" t="s">
         <v>17</v>
@@ -5516,40 +5524,40 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>40483</v>
+        <v>40513</v>
       </c>
       <c r="B83" s="7">
-        <v>13.8</v>
+        <v>13.1</v>
       </c>
       <c r="C83" s="7">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="D83" s="7">
-        <v>13.7</v>
+        <v>15.1</v>
       </c>
       <c r="E83" s="7">
-        <v>13</v>
-      </c>
-      <c r="F83" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-5.07</v>
+        <v>12.7</v>
+      </c>
+      <c r="F83" s="8">
+        <v>2</v>
+      </c>
+      <c r="G83" s="8">
+        <v>15.27</v>
       </c>
       <c r="H83" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="I83" s="8">
-        <v>9.76</v>
+        <v>0.433</v>
+      </c>
+      <c r="I83" s="10">
+        <v>-9.4700000000000006</v>
       </c>
       <c r="J83" s="10">
-        <v>-3.11</v>
+        <v>-51.9</v>
       </c>
       <c r="K83" s="9">
-        <v>5.27</v>
+        <v>5.7</v>
       </c>
       <c r="L83" s="8">
-        <v>19.399999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="M83" s="9" t="s">
         <v>17</v>
@@ -5569,40 +5577,40 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>40452</v>
+        <v>40483</v>
       </c>
       <c r="B84" s="7">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="C84" s="7">
-        <v>13.8</v>
+        <v>13.1</v>
       </c>
       <c r="D84" s="7">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="E84" s="7">
-        <v>13.4</v>
-      </c>
-      <c r="F84" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="G84" s="8">
-        <v>1.47</v>
+        <v>13</v>
+      </c>
+      <c r="F84" s="10">
+        <v>-0.7</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-5.07</v>
       </c>
       <c r="H84" s="9">
-        <v>0.435</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="I84" s="8">
-        <v>2.7</v>
+        <v>9.76</v>
       </c>
       <c r="J84" s="10">
-        <v>-16.5</v>
+        <v>-3.11</v>
       </c>
       <c r="K84" s="9">
-        <v>4.79</v>
+        <v>5.27</v>
       </c>
       <c r="L84" s="8">
-        <v>22.3</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="M84" s="9" t="s">
         <v>17</v>
@@ -5622,40 +5630,40 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>40422</v>
+        <v>40452</v>
       </c>
       <c r="B85" s="7">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="C85" s="7">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="D85" s="7">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="E85" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="F85" s="10">
-        <v>-0.65</v>
-      </c>
-      <c r="G85" s="10">
-        <v>-4.5599999999999996</v>
+        <v>13.4</v>
+      </c>
+      <c r="F85" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="G85" s="8">
+        <v>1.47</v>
       </c>
       <c r="H85" s="9">
-        <v>0.42399999999999999</v>
-      </c>
-      <c r="I85" s="10">
-        <v>-15.8</v>
+        <v>0.435</v>
+      </c>
+      <c r="I85" s="8">
+        <v>2.7</v>
       </c>
       <c r="J85" s="10">
-        <v>-9.44</v>
+        <v>-16.5</v>
       </c>
       <c r="K85" s="9">
-        <v>4.3499999999999996</v>
+        <v>4.79</v>
       </c>
       <c r="L85" s="8">
-        <v>28.2</v>
+        <v>22.3</v>
       </c>
       <c r="M85" s="9" t="s">
         <v>17</v>
@@ -5675,40 +5683,40 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>40391</v>
+        <v>40422</v>
       </c>
       <c r="B86" s="7">
-        <v>16.8</v>
+        <v>14.25</v>
       </c>
       <c r="C86" s="7">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="D86" s="7">
-        <v>18</v>
+        <v>14.8</v>
       </c>
       <c r="E86" s="7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="F86" s="10">
-        <v>-3.55</v>
+        <v>-0.65</v>
       </c>
       <c r="G86" s="10">
-        <v>-19.940000000000001</v>
+        <v>-4.5599999999999996</v>
       </c>
       <c r="H86" s="9">
-        <v>0.504</v>
-      </c>
-      <c r="I86" s="8">
-        <v>16.2</v>
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="I86" s="10">
+        <v>-15.8</v>
       </c>
       <c r="J86" s="10">
-        <v>-1.6</v>
+        <v>-9.44</v>
       </c>
       <c r="K86" s="9">
-        <v>3.93</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="L86" s="8">
-        <v>34.299999999999997</v>
+        <v>28.2</v>
       </c>
       <c r="M86" s="9" t="s">
         <v>17</v>
@@ -5728,40 +5736,40 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>40360</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>17</v>
+        <v>40391</v>
+      </c>
+      <c r="B87" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="C87" s="7">
+        <v>14.25</v>
+      </c>
+      <c r="D87" s="7">
+        <v>18</v>
+      </c>
+      <c r="E87" s="7">
+        <v>14</v>
+      </c>
+      <c r="F87" s="10">
+        <v>-3.55</v>
+      </c>
+      <c r="G87" s="10">
+        <v>-19.940000000000001</v>
       </c>
       <c r="H87" s="9">
-        <v>0.434</v>
-      </c>
-      <c r="I87" s="10">
-        <v>-19.5</v>
+        <v>0.504</v>
+      </c>
+      <c r="I87" s="8">
+        <v>16.2</v>
       </c>
       <c r="J87" s="10">
-        <v>-16.7</v>
+        <v>-1.6</v>
       </c>
       <c r="K87" s="9">
-        <v>3.42</v>
+        <v>3.93</v>
       </c>
       <c r="L87" s="8">
-        <v>41.9</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="M87" s="9" t="s">
         <v>17</v>
@@ -5781,7 +5789,7 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>40330</v>
+        <v>40360</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5802,19 +5810,19 @@
         <v>17</v>
       </c>
       <c r="H88" s="9">
-        <v>0.53900000000000003</v>
-      </c>
-      <c r="I88" s="8">
-        <v>2.85</v>
-      </c>
-      <c r="J88" s="8">
-        <v>31</v>
+        <v>0.434</v>
+      </c>
+      <c r="I88" s="10">
+        <v>-19.5</v>
+      </c>
+      <c r="J88" s="10">
+        <v>-16.7</v>
       </c>
       <c r="K88" s="9">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="L88" s="8">
-        <v>58</v>
+        <v>41.9</v>
       </c>
       <c r="M88" s="9" t="s">
         <v>17</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>40299</v>
+        <v>40330</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>17</v>
@@ -5855,19 +5863,19 @@
         <v>17</v>
       </c>
       <c r="H89" s="9">
-        <v>0.52400000000000002</v>
-      </c>
-      <c r="I89" s="10">
-        <v>-7.67</v>
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="I89" s="8">
+        <v>2.85</v>
       </c>
       <c r="J89" s="8">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="K89" s="9">
-        <v>2.4500000000000002</v>
+        <v>2.99</v>
       </c>
       <c r="L89" s="8">
-        <v>65.5</v>
+        <v>58</v>
       </c>
       <c r="M89" s="9" t="s">
         <v>17</v>
@@ -5887,7 +5895,7 @@
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>40269</v>
+        <v>40299</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>17</v>
@@ -5908,19 +5916,19 @@
         <v>17</v>
       </c>
       <c r="H90" s="9">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="I90" s="8">
-        <v>23.4</v>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="I90" s="10">
+        <v>-7.67</v>
       </c>
       <c r="J90" s="8">
-        <v>13.2</v>
+        <v>30.1</v>
       </c>
       <c r="K90" s="9">
-        <v>1.93</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="L90" s="8">
-        <v>78.8</v>
+        <v>65.5</v>
       </c>
       <c r="M90" s="9" t="s">
         <v>17</v>
@@ -5940,7 +5948,7 @@
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>40238</v>
+        <v>40269</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>17</v>
@@ -5961,19 +5969,19 @@
         <v>17</v>
       </c>
       <c r="H91" s="9">
-        <v>0.46</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="I91" s="8">
-        <v>1.46</v>
+        <v>23.4</v>
       </c>
       <c r="J91" s="8">
-        <v>41.6</v>
+        <v>13.2</v>
       </c>
       <c r="K91" s="9">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="L91" s="8">
-        <v>135.6</v>
+        <v>78.8</v>
       </c>
       <c r="M91" s="9" t="s">
         <v>17</v>
@@ -5993,7 +6001,7 @@
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>40210</v>
+        <v>40238</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>17</v>
@@ -6014,19 +6022,19 @@
         <v>17</v>
       </c>
       <c r="H92" s="9">
-        <v>0.45300000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I92" s="8">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="J92" s="8">
-        <v>181.6</v>
+        <v>41.6</v>
       </c>
       <c r="K92" s="9">
-        <v>0.90100000000000002</v>
+        <v>1.36</v>
       </c>
       <c r="L92" s="8">
-        <v>256.10000000000002</v>
+        <v>135.6</v>
       </c>
       <c r="M92" s="9" t="s">
         <v>17</v>
@@ -6046,7 +6054,7 @@
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>40179</v>
+        <v>40210</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6067,19 +6075,19 @@
         <v>17</v>
       </c>
       <c r="H93" s="9">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="I93" s="10">
-        <v>-50.2</v>
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="I93" s="8">
+        <v>1.17</v>
       </c>
       <c r="J93" s="8">
-        <v>386.3</v>
+        <v>181.6</v>
       </c>
       <c r="K93" s="9">
-        <v>0.44800000000000001</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="L93" s="8">
-        <v>386.3</v>
+        <v>256.10000000000002</v>
       </c>
       <c r="M93" s="9" t="s">
         <v>17</v>
@@ -6099,7 +6107,7 @@
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>40148</v>
+        <v>40179</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6120,19 +6128,19 @@
         <v>17</v>
       </c>
       <c r="H94" s="9">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="I94" s="8">
-        <v>82.2</v>
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="I94" s="10">
+        <v>-50.2</v>
       </c>
       <c r="J94" s="8">
-        <v>413.1</v>
+        <v>386.3</v>
       </c>
       <c r="K94" s="9">
-        <v>5.31</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="L94" s="8">
-        <v>11.9</v>
+        <v>386.3</v>
       </c>
       <c r="M94" s="9" t="s">
         <v>17</v>
@@ -6152,7 +6160,7 @@
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>40118</v>
+        <v>40148</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6173,19 +6181,19 @@
         <v>17</v>
       </c>
       <c r="H95" s="9">
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="I95" s="10">
-        <v>-5.42</v>
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="I95" s="8">
+        <v>82.2</v>
       </c>
       <c r="J95" s="8">
-        <v>38.5</v>
+        <v>413.1</v>
       </c>
       <c r="K95" s="9">
-        <v>4.41</v>
-      </c>
-      <c r="L95" s="10">
-        <v>-3.49</v>
+        <v>5.31</v>
+      </c>
+      <c r="L95" s="8">
+        <v>11.9</v>
       </c>
       <c r="M95" s="9" t="s">
         <v>17</v>
@@ -6205,7 +6213,7 @@
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>40087</v>
+        <v>40118</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6226,19 +6234,19 @@
         <v>17</v>
       </c>
       <c r="H96" s="9">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="I96" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="J96" s="10">
-        <v>-3.68</v>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="I96" s="10">
+        <v>-5.42</v>
+      </c>
+      <c r="J96" s="8">
+        <v>38.5</v>
       </c>
       <c r="K96" s="9">
-        <v>3.91</v>
+        <v>4.41</v>
       </c>
       <c r="L96" s="10">
-        <v>-7.04</v>
+        <v>-3.49</v>
       </c>
       <c r="M96" s="9" t="s">
         <v>17</v>
@@ -6258,7 +6266,7 @@
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>40057</v>
+        <v>40087</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>17</v>
@@ -6279,19 +6287,19 @@
         <v>17</v>
       </c>
       <c r="H97" s="9">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="I97" s="10">
-        <v>-8.57</v>
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="I97" s="8">
+        <v>11.4</v>
       </c>
       <c r="J97" s="10">
-        <v>-11</v>
+        <v>-3.68</v>
       </c>
       <c r="K97" s="9">
-        <v>3.39</v>
+        <v>3.91</v>
       </c>
       <c r="L97" s="10">
-        <v>-7.53</v>
+        <v>-7.04</v>
       </c>
       <c r="M97" s="9" t="s">
         <v>17</v>
@@ -6311,54 +6319,107 @@
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
+        <v>40057</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H98" s="9">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="I98" s="10">
+        <v>-8.57</v>
+      </c>
+      <c r="J98" s="10">
+        <v>-11</v>
+      </c>
+      <c r="K98" s="9">
+        <v>3.39</v>
+      </c>
+      <c r="L98" s="10">
+        <v>-7.53</v>
+      </c>
+      <c r="M98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q98" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
         <v>40026</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H98" s="9">
+      <c r="B99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" s="9">
         <v>0.51200000000000001</v>
       </c>
-      <c r="I98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="8">
+      <c r="I99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="8">
         <v>47</v>
       </c>
-      <c r="K98" s="9">
+      <c r="K99" s="9">
         <v>2.93</v>
       </c>
-      <c r="L98" s="10">
+      <c r="L99" s="10">
         <v>-6.95</v>
       </c>
-      <c r="M98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q98" s="9" t="s">
+      <c r="M99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q99" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6377,7 +6438,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>